--- a/2026/10. 8 Juli 2026 - Rapat Kesantrian/JADWAL MPLM 2025-2026.xlsx
+++ b/2026/10. 8 Juli 2026 - Rapat Kesantrian/JADWAL MPLM 2025-2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15360" windowHeight="7380" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="juli 2025" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'juli 2025'!$A$1:$E$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'juli 2026'!$A$1:$E$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2292,7 +2293,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
@@ -3201,7 +3204,9 @@
     <mergeCell ref="A28:A48"/>
     <mergeCell ref="A50:A70"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" scale="60" fitToHeight="0" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>